--- a/data/raw/aggregators/AHSTAT/JPN.xlsx
+++ b/data/raw/aggregators/AHSTAT/JPN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lehbib\Documents\GitHub\Global-Macro-Project\data\raw\country_level\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lehbib\Documents\GitHub\Global-Macro-Project\data\raw\aggregators\AHSTAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2140A5FC-4B14-4A61-A2CC-8EEDDB4C379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88ADB7E2-C2CF-4CC9-A082-55D553BF50ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{F512589D-9F2E-44AD-9B09-3295B30D59A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F512589D-9F2E-44AD-9B09-3295B30D59A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="160">
   <si>
     <t>year</t>
   </si>
@@ -523,6 +523,12 @@
   </si>
   <si>
     <t>person</t>
+  </si>
+  <si>
+    <t>Government Revenue</t>
+  </si>
+  <si>
+    <t>Government Tax Revenue</t>
   </si>
 </sst>
 </file>
@@ -931,16 +937,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EED724-A2A5-48DD-B872-DBBD6B1D2467}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -966,7 +972,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -989,7 +995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1035,7 +1041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1107,7 +1113,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1197,7 +1203,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1258,7 +1264,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1284,7 +1290,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1397,7 +1403,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -1472,7 +1478,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
         <v>58</v>
@@ -1498,7 +1504,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1506,7 +1512,7 @@
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
         <v>58</v>
@@ -1524,7 +1530,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
@@ -1550,7 +1556,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1558,7 +1564,7 @@
         <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="D24" t="s">
         <v>58</v>
@@ -1573,7 +1579,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1619,7 +1625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -1645,7 +1651,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -1668,7 +1674,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -1694,7 +1700,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -1717,7 +1723,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -1740,7 +1746,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -1763,7 +1769,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1789,7 +1795,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -1821,9 +1827,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D2C538-A529-4E06-A5FD-A36F10DFB834}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1831,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1847,9 +1853,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92A04FA-F18B-4A99-B473-AA8A5FA51529}">
   <dimension ref="A1:C88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1885</v>
       </c>
@@ -1871,7 +1877,7 @@
         <v>3852</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1886</v>
       </c>
@@ -1882,7 +1888,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1887</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>4342</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1888</v>
       </c>
@@ -1904,7 +1910,7 @@
         <v>4449</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1889</v>
       </c>
@@ -1915,7 +1921,7 @@
         <v>4722</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1890</v>
       </c>
@@ -1926,7 +1932,7 @@
         <v>4583</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1891</v>
       </c>
@@ -1937,7 +1943,7 @@
         <v>5033</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1892</v>
       </c>
@@ -1948,7 +1954,7 @@
         <v>4949</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1893</v>
       </c>
@@ -1959,7 +1965,7 @@
         <v>5227</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1894</v>
       </c>
@@ -1970,7 +1976,7 @@
         <v>5459</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1895</v>
       </c>
@@ -1981,7 +1987,7 @@
         <v>5798</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1896</v>
       </c>
@@ -1992,7 +1998,7 @@
         <v>5773</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1897</v>
       </c>
@@ -2003,7 +2009,7 @@
         <v>5701</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1898</v>
       </c>
@@ -2014,7 +2020,7 @@
         <v>5907</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1899</v>
       </c>
@@ -2025,7 +2031,7 @@
         <v>6318</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1900</v>
       </c>
@@ -2036,7 +2042,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1901</v>
       </c>
@@ -2047,7 +2053,7 @@
         <v>6469</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1902</v>
       </c>
@@ -2058,7 +2064,7 @@
         <v>6358</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1903</v>
       </c>
@@ -2069,7 +2075,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1904</v>
       </c>
@@ -2080,7 +2086,7 @@
         <v>7084</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1905</v>
       </c>
@@ -2091,7 +2097,7 @@
         <v>6769</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1906</v>
       </c>
@@ -2102,7 +2108,7 @@
         <v>6733</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1907</v>
       </c>
@@ -2113,7 +2119,7 @@
         <v>6991</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1908</v>
       </c>
@@ -2124,7 +2130,7 @@
         <v>7187</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1909</v>
       </c>
@@ -2135,7 +2141,7 @@
         <v>7357</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1910</v>
       </c>
@@ -2146,7 +2152,7 @@
         <v>7834</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1911</v>
       </c>
@@ -2157,7 +2163,7 @@
         <v>7922</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1912</v>
       </c>
@@ -2168,7 +2174,7 @@
         <v>7927</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1913</v>
       </c>
@@ -2179,7 +2185,7 @@
         <v>8001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1914</v>
       </c>
@@ -2190,7 +2196,7 @@
         <v>8061</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1915</v>
       </c>
@@ -2201,7 +2207,7 @@
         <v>8527</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1916</v>
       </c>
@@ -2212,7 +2218,7 @@
         <v>9233</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1917</v>
       </c>
@@ -2223,7 +2229,7 @@
         <v>10061</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1918</v>
       </c>
@@ -2234,7 +2240,7 @@
         <v>10929</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1919</v>
       </c>
@@ -2245,7 +2251,7 @@
         <v>11475</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1920</v>
       </c>
@@ -2256,7 +2262,7 @@
         <v>11422</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1921</v>
       </c>
@@ -2267,7 +2273,7 @@
         <v>12153</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1922</v>
       </c>
@@ -2278,7 +2284,7 @@
         <v>11831</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1923</v>
       </c>
@@ -2289,7 +2295,7 @@
         <v>11292</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1924</v>
       </c>
@@ -2300,7 +2306,7 @@
         <v>12704</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1925</v>
       </c>
@@ -2311,7 +2317,7 @@
         <v>12332</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1926</v>
       </c>
@@ -2322,7 +2328,7 @@
         <v>12424</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1927</v>
       </c>
@@ -2333,7 +2339,7 @@
         <v>12843</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1928</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>13673</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1929</v>
       </c>
@@ -2355,7 +2361,7 @@
         <v>13735</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1930</v>
       </c>
@@ -2366,7 +2372,7 @@
         <v>13882</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1931</v>
       </c>
@@ -2377,7 +2383,7 @@
         <v>13941</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1932</v>
       </c>
@@ -2388,7 +2394,7 @@
         <v>14557</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1933</v>
       </c>
@@ -2399,7 +2405,7 @@
         <v>16025</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1934</v>
       </c>
@@ -2410,7 +2416,7 @@
         <v>17422</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1935</v>
       </c>
@@ -2421,7 +2427,7 @@
         <v>18366</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1936</v>
       </c>
@@ -2432,7 +2438,7 @@
         <v>18763</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1937</v>
       </c>
@@ -2443,7 +2449,7 @@
         <v>19949</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1938</v>
       </c>
@@ -2454,7 +2460,7 @@
         <v>20714</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1939</v>
       </c>
@@ -2465,7 +2471,7 @@
         <v>21954</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1940</v>
       </c>
@@ -2476,7 +2482,7 @@
         <v>22848</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1941</v>
       </c>
@@ -2484,7 +2490,7 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1942</v>
       </c>
@@ -2492,7 +2498,7 @@
         <v>54384</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1943</v>
       </c>
@@ -2500,7 +2506,7 @@
         <v>63824</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1944</v>
       </c>
@@ -2508,12 +2514,12 @@
         <v>74503</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1945</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1946</v>
       </c>
@@ -2521,7 +2527,7 @@
         <v>474000</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1947</v>
       </c>
@@ -2529,7 +2535,7 @@
         <v>1309000</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1948</v>
       </c>
@@ -2537,7 +2543,7 @@
         <v>2666000</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1949</v>
       </c>
@@ -2545,7 +2551,7 @@
         <v>3375000</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1950</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>3947000</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1951</v>
       </c>
@@ -2561,7 +2567,7 @@
         <v>5444000</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1952</v>
       </c>
@@ -2569,7 +2575,7 @@
         <v>6263000</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1953</v>
       </c>
@@ -2577,7 +2583,7 @@
         <v>7055000</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1954</v>
       </c>
@@ -2585,7 +2591,7 @@
         <v>7831000</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1955</v>
       </c>
@@ -2593,7 +2599,7 @@
         <v>8624000</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1956</v>
       </c>
@@ -2601,7 +2607,7 @@
         <v>9726000</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1957</v>
       </c>
@@ -2609,7 +2615,7 @@
         <v>11080000</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1958</v>
       </c>
@@ -2617,7 +2623,7 @@
         <v>11522000</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1959</v>
       </c>
@@ -2625,7 +2631,7 @@
         <v>12926000</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1960</v>
       </c>
@@ -2633,7 +2639,7 @@
         <v>15499000</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1961</v>
       </c>
@@ -2641,7 +2647,7 @@
         <v>19126000</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1962</v>
       </c>
@@ -2649,7 +2655,7 @@
         <v>21199000</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1963</v>
       </c>
@@ -2657,7 +2663,7 @@
         <v>24464000</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1964</v>
       </c>
@@ -2665,7 +2671,7 @@
         <v>28921000</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1965</v>
       </c>
@@ -2673,7 +2679,7 @@
         <v>31962000</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1966</v>
       </c>
@@ -2681,7 +2687,7 @@
         <v>36796000</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1967</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>43545000</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1968</v>
       </c>
@@ -2697,7 +2703,7 @@
         <v>51708000</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1969</v>
       </c>
@@ -2705,7 +2711,7 @@
         <v>60242000</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1970</v>
       </c>
@@ -2713,7 +2719,7 @@
         <v>70985000</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1971</v>
       </c>
@@ -2729,12 +2735,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA687C28-50EF-4AF0-913B-A20830B74D17}">
   <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2745,7 +2751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1871</v>
       </c>
@@ -2753,7 +2759,7 @@
         <v>34269471</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1872</v>
       </c>
@@ -2764,7 +2770,7 @@
         <v>21390800</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1873</v>
       </c>
@@ -2775,7 +2781,7 @@
         <v>21420200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1874</v>
       </c>
@@ -2786,7 +2792,7 @@
         <v>21445500</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1875</v>
       </c>
@@ -2797,7 +2803,7 @@
         <v>21490700</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1876</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>21583100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1877</v>
       </c>
@@ -2819,7 +2825,7 @@
         <v>21692000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1878</v>
       </c>
@@ -2830,7 +2836,7 @@
         <v>21788600</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1879</v>
       </c>
@@ -2841,7 +2847,7 @@
         <v>21844600</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1880</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>21854900</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1881</v>
       </c>
@@ -2863,7 +2869,7 @@
         <v>21918700</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1882</v>
       </c>
@@ -2874,7 +2880,7 @@
         <v>21928900</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1883</v>
       </c>
@@ -2885,7 +2891,7 @@
         <v>22020500</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1884</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>22171800</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1885</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>22317700</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1886</v>
       </c>
@@ -2918,7 +2924,7 @@
         <v>22359200</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1887</v>
       </c>
@@ -2929,7 +2935,7 @@
         <v>22378900</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1888</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>22557800</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1889</v>
       </c>
@@ -2951,7 +2957,7 @@
         <v>22761500</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1890</v>
       </c>
@@ -2962,7 +2968,7 @@
         <v>22946100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1891</v>
       </c>
@@ -2973,7 +2979,7 @@
         <v>23092600</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1892</v>
       </c>
@@ -2984,7 +2990,7 @@
         <v>23240300</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1893</v>
       </c>
@@ -2995,7 +3001,7 @@
         <v>23364000</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1894</v>
       </c>
@@ -3006,7 +3012,7 @@
         <v>23489100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1895</v>
       </c>
@@ -3017,7 +3023,7 @@
         <v>23589100</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1896</v>
       </c>
@@ -3028,7 +3034,7 @@
         <v>23727000</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1897</v>
       </c>
@@ -3039,7 +3045,7 @@
         <v>23878000</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1898</v>
       </c>
@@ -3050,7 +3056,7 @@
         <v>24040300</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1899</v>
       </c>
@@ -3061,7 +3067,7 @@
         <v>24144800</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1900</v>
       </c>
@@ -3072,7 +3078,7 @@
         <v>24251700</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1901</v>
       </c>
@@ -3083,7 +3089,7 @@
         <v>24367000</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1902</v>
       </c>
@@ -3094,7 +3100,7 @@
         <v>24481000</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1903</v>
       </c>
@@ -3105,7 +3111,7 @@
         <v>24632400</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1904</v>
       </c>
@@ -3116,7 +3122,7 @@
         <v>24763600</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1905</v>
       </c>
@@ -3127,7 +3133,7 @@
         <v>24824300</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1906</v>
       </c>
@@ -3138,7 +3144,7 @@
         <v>24928400</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1907</v>
       </c>
@@ -3149,7 +3155,7 @@
         <v>25072500</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1908</v>
       </c>
@@ -3160,7 +3166,7 @@
         <v>25156800</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1909</v>
       </c>
@@ -3171,7 +3177,7 @@
         <v>25197500</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1910</v>
       </c>
@@ -3182,7 +3188,7 @@
         <v>25266800</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1911</v>
       </c>
@@ -3193,7 +3199,7 @@
         <v>25393800</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1912</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>25573300</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1913</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>25751300</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1914</v>
       </c>
@@ -3226,7 +3232,7 @@
         <v>25942600</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1915</v>
       </c>
@@ -3237,7 +3243,7 @@
         <v>26123200</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1916</v>
       </c>
@@ -3248,7 +3254,7 @@
         <v>26386900</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1917</v>
       </c>
@@ -3259,7 +3265,7 @@
         <v>26594300</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1918</v>
       </c>
@@ -3270,7 +3276,7 @@
         <v>26756800</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1919</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>26779600</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1920</v>
       </c>
@@ -3292,7 +3298,7 @@
         <v>27261100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1921</v>
       </c>
@@ -3303,7 +3309,7 @@
         <v>27397000</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1922</v>
       </c>
@@ -3314,7 +3320,7 @@
         <v>27616100</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1923</v>
       </c>
@@ -3325,7 +3331,7 @@
         <v>27830500</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1924</v>
       </c>
@@ -3336,7 +3342,7 @@
         <v>28075900</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1925</v>
       </c>
@@ -3347,7 +3353,7 @@
         <v>28301100</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1926</v>
       </c>
@@ -3358,7 +3364,7 @@
         <v>28564500</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1927</v>
       </c>
@@ -3369,7 +3375,7 @@
         <v>28820200</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1928</v>
       </c>
@@ -3380,7 +3386,7 @@
         <v>29061800</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1929</v>
       </c>
@@ -3391,7 +3397,7 @@
         <v>29312100</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1930</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>29619600</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1931</v>
       </c>
@@ -3413,7 +3419,7 @@
         <v>29951900</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1932</v>
       </c>
@@ -3424,7 +3430,7 @@
         <v>30214600</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1933</v>
       </c>
@@ -3435,7 +3441,7 @@
         <v>30670700</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1934</v>
       </c>
@@ -3446,7 +3452,7 @@
         <v>31084300</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1935</v>
       </c>
@@ -3457,7 +3463,7 @@
         <v>31644900</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1936</v>
       </c>
@@ -3468,7 +3474,7 @@
         <v>32059000</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1937</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>32156100</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1938</v>
       </c>
@@ -3490,7 +3496,7 @@
         <v>32289700</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1939</v>
       </c>
@@ -3501,7 +3507,7 @@
         <v>32652300</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1940</v>
       </c>
@@ -3520,9 +3526,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C0B992-C1E4-4755-94A0-31FFB052B4E8}">
   <dimension ref="B2:Q65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>108</v>
@@ -3542,7 +3548,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
         <v>109</v>
@@ -3562,7 +3568,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="5">
         <v>31842</v>
@@ -3610,7 +3616,7 @@
         <v>31856</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="5">
         <v>1</v>
@@ -3658,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
         <v>110</v>
@@ -3706,7 +3712,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>125</v>
@@ -3754,7 +3760,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
         <v>140</v>
@@ -3802,7 +3808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="5">
         <v>1871</v>
@@ -3850,7 +3856,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="5">
         <v>1920</v>
@@ -3898,7 +3904,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>154</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>156</v>
       </c>
@@ -3998,7 +4004,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>1871</v>
       </c>
@@ -4048,7 +4054,7 @@
         <v>34269471</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>1872</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>34450897</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>1873</v>
       </c>
@@ -4148,7 +4154,7 @@
         <v>34624889</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>1874</v>
       </c>
@@ -4198,7 +4204,7 @@
         <v>34791807</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>1875</v>
       </c>
@@ -4248,7 +4254,7 @@
         <v>35036567</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>1876</v>
       </c>
@@ -4298,7 +4304,7 @@
         <v>35358865</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>1877</v>
       </c>
@@ -4348,7 +4354,7 @@
         <v>35662663</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>1878</v>
       </c>
@@ -4398,7 +4404,7 @@
         <v>35968803</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>1879</v>
       </c>
@@ -4448,7 +4454,7 @@
         <v>36164709</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>1880</v>
       </c>
@@ -4498,7 +4504,7 @@
         <v>36489790</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="5">
         <v>1881</v>
       </c>
@@ -4548,7 +4554,7 @@
         <v>36793228</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" s="5">
         <v>1882</v>
       </c>
@@ -4598,7 +4604,7 @@
         <v>37112203</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="5">
         <v>1883</v>
       </c>
@@ -4648,7 +4654,7 @@
         <v>37520505</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>1884</v>
       </c>
@@ -4698,7 +4704,7 @@
         <v>37877643</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="5">
         <v>1885</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>38176457</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="5">
         <v>1886</v>
       </c>
@@ -4798,7 +4804,7 @@
         <v>38289042</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" s="5">
         <v>1887</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>38626847</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>1888</v>
       </c>
@@ -4898,7 +4904,7 @@
         <v>39081711</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>1889</v>
       </c>
@@ -4948,7 +4954,7 @@
         <v>39516174</v>
       </c>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>1890</v>
       </c>
@@ -4998,7 +5004,7 @@
         <v>39868868</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>1891</v>
       </c>
@@ -5048,7 +5054,7 @@
         <v>40134870</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>1892</v>
       </c>
@@ -5098,7 +5104,7 @@
         <v>40500236</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>1893</v>
       </c>
@@ -5148,7 +5154,7 @@
         <v>40791927</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>1894</v>
       </c>
@@ -5198,7 +5204,7 @@
         <v>41211672</v>
       </c>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B40" s="5">
         <v>1895</v>
       </c>
@@ -5248,7 +5254,7 @@
         <v>41650245</v>
       </c>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>1896</v>
       </c>
@@ -5298,7 +5304,7 @@
         <v>42067053</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>1897</v>
       </c>
@@ -5348,7 +5354,7 @@
         <v>42559522</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>1898</v>
       </c>
@@ -5398,7 +5404,7 @@
         <v>43075547</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="5">
         <v>1899</v>
       </c>
@@ -5448,7 +5454,7 @@
         <v>43520895</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B45" s="5">
         <v>1900</v>
       </c>
@@ -5498,7 +5504,7 @@
         <v>44056240</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B46" s="5">
         <v>1901</v>
       </c>
@@ -5548,7 +5554,7 @@
         <v>44662657</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="5">
         <v>1902</v>
       </c>
@@ -5598,7 +5604,7 @@
         <v>45246208</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B48" s="5">
         <v>1903</v>
       </c>
@@ -5648,7 +5654,7 @@
         <v>45856439</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" s="5">
         <v>1904</v>
       </c>
@@ -5698,7 +5704,7 @@
         <v>46343317</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B50" s="5">
         <v>1905</v>
       </c>
@@ -5748,7 +5754,7 @@
         <v>46746940</v>
       </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B51" s="5">
         <v>1906</v>
       </c>
@@ -5798,7 +5804,7 @@
         <v>47131377</v>
       </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B52" s="5">
         <v>1907</v>
       </c>
@@ -5848,7 +5854,7 @@
         <v>47654001</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B53" s="5">
         <v>1908</v>
       </c>
@@ -5898,7 +5904,7 @@
         <v>48225368</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B54" s="5">
         <v>1909</v>
       </c>
@@ -5948,7 +5954,7 @@
         <v>48850735</v>
       </c>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B55" s="5">
         <v>1910</v>
       </c>
@@ -5998,7 +6004,7 @@
         <v>49488599</v>
       </c>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B56" s="5">
         <v>1911</v>
       </c>
@@ -6048,7 +6054,7 @@
         <v>50178398</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B57" s="5">
         <v>1912</v>
       </c>
@@ -6098,7 +6104,7 @@
         <v>50925427</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B58" s="5">
         <v>1913</v>
       </c>
@@ -6148,7 +6154,7 @@
         <v>51672473</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" s="5">
         <v>1914</v>
       </c>
@@ -6198,7 +6204,7 @@
         <v>52387547</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B60" s="5">
         <v>1915</v>
       </c>
@@ -6248,7 +6254,7 @@
         <v>53109781</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B61" s="5">
         <v>1916</v>
       </c>
@@ -6298,7 +6304,7 @@
         <v>53767746</v>
       </c>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B62" s="5">
         <v>1917</v>
       </c>
@@ -6348,7 +6354,7 @@
         <v>54365876</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B63" s="5">
         <v>1918</v>
       </c>
@@ -6398,7 +6404,7 @@
         <v>54710686</v>
       </c>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B64" s="5">
         <v>1919</v>
       </c>
@@ -6448,7 +6454,7 @@
         <v>55032672</v>
       </c>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B65" s="5">
         <v>1920</v>
       </c>
@@ -6506,9 +6512,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1401EA-FD07-4F99-B071-57102B64931C}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6516,7 +6522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1868</v>
       </c>
@@ -6524,7 +6530,7 @@
         <v>1.9319999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1869</v>
       </c>
@@ -6532,7 +6538,7 @@
         <v>3.4169999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1870</v>
       </c>
@@ -6540,7 +6546,7 @@
         <v>3.6560000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1871</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>3.944</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1872</v>
       </c>
@@ -6556,7 +6562,7 @@
         <v>5.4139999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1873</v>
       </c>
@@ -6564,7 +6570,7 @@
         <v>7.2370000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1874</v>
       </c>
@@ -6572,7 +6578,7 @@
         <v>11.08</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1875</v>
       </c>
@@ -6580,7 +6586,7 @@
         <v>14.505000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1876</v>
       </c>
@@ -6588,7 +6594,7 @@
         <v>12.58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1877</v>
       </c>
@@ -6596,7 +6602,7 @@
         <v>16.146000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1878</v>
       </c>
@@ -6604,7 +6610,7 @@
         <v>16.271000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1879</v>
       </c>
@@ -6612,7 +6618,7 @@
         <v>16.202999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1880</v>
       </c>
@@ -6620,7 +6626,7 @@
         <v>20.515000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1881</v>
       </c>
@@ -6628,7 +6634,7 @@
         <v>21.035</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1882</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>20.195</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1883</v>
       </c>
@@ -6644,7 +6650,7 @@
         <v>25.145</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1884</v>
       </c>
@@ -6652,7 +6658,7 @@
         <v>27.271999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1885</v>
       </c>
@@ -6660,7 +6666,7 @@
         <v>30.684000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1886</v>
       </c>
@@ -6668,7 +6674,7 @@
         <v>28.402999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1887</v>
       </c>
@@ -6676,7 +6682,7 @@
         <v>44.956000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1888</v>
       </c>
@@ -6684,7 +6690,7 @@
         <v>75.819999999999993</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1889</v>
       </c>
@@ -6692,7 +6698,7 @@
         <v>76.313000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1890</v>
       </c>
@@ -6700,7 +6706,7 @@
         <v>83.515000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1891</v>
       </c>
@@ -6708,7 +6714,7 @@
         <v>90.283000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1892</v>
       </c>
@@ -6716,7 +6722,7 @@
         <v>77.150999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1893</v>
       </c>
@@ -6724,7 +6730,7 @@
         <v>94.637</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1894</v>
       </c>
@@ -6732,7 +6738,7 @@
         <v>143.625</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1895</v>
       </c>
@@ -6740,7 +6746,7 @@
         <v>154.30500000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1896</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>201.41200000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1897</v>
       </c>
@@ -6756,7 +6762,7 @@
         <v>292.94799999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1898</v>
       </c>
@@ -6764,7 +6770,7 @@
         <v>305.779</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1899</v>
       </c>
@@ -6772,7 +6778,7 @@
         <v>259.56400000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1900</v>
       </c>
@@ -6780,7 +6786,7 @@
         <v>273.315</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1901</v>
       </c>
@@ -6788,7 +6794,7 @@
         <v>260.90600000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1902</v>
       </c>
@@ -6796,7 +6802,7 @@
         <v>215.59700000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1903</v>
       </c>
@@ -6804,7 +6810,7 @@
         <v>235.095</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1904</v>
       </c>
@@ -6812,7 +6818,7 @@
         <v>259.77</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1905</v>
       </c>
@@ -6820,7 +6826,7 @@
         <v>345.14299999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1906</v>
       </c>
@@ -6828,7 +6834,7 @@
         <v>341.64600000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1907</v>
       </c>
@@ -6836,7 +6842,7 @@
         <v>423.709</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1908</v>
       </c>
@@ -6844,7 +6850,7 @@
         <v>458.17200000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1909</v>
       </c>
@@ -6852,7 +6858,7 @@
         <v>392.28500000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1910</v>
       </c>
@@ -6860,7 +6866,7 @@
         <v>491.50299999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1911</v>
       </c>
@@ -6868,7 +6874,7 @@
         <v>660.55700000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1912</v>
       </c>
@@ -6876,7 +6882,7 @@
         <v>643.46699999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1913</v>
       </c>
@@ -6884,7 +6890,7 @@
         <v>628.91</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1914</v>
       </c>
@@ -6892,7 +6898,7 @@
         <v>576.553</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1915</v>
       </c>
@@ -6900,7 +6906,7 @@
         <v>610.46500000000003</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1916</v>
       </c>
@@ -6908,7 +6914,7 @@
         <v>870.31200000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1917</v>
       </c>
@@ -6916,7 +6922,7 @@
         <v>1584.9390000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1918</v>
       </c>
@@ -6924,7 +6930,7 @@
         <v>2269.6559999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1919</v>
       </c>
@@ -6932,7 +6938,7 @@
         <v>2657.9969999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1920</v>
       </c>
@@ -6940,7 +6946,7 @@
         <v>3258.5790000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1921</v>
       </c>
@@ -6948,7 +6954,7 @@
         <v>2678.1010000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1922</v>
       </c>
@@ -6956,7 +6962,7 @@
         <v>2740.665</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1923</v>
       </c>
@@ -6964,7 +6970,7 @@
         <v>2081.8969999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1924</v>
       </c>
@@ -6972,7 +6978,7 @@
         <v>2543.8739999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1925</v>
       </c>
@@ -6980,7 +6986,7 @@
         <v>2381.502</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1926</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>2598.5700000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1927</v>
       </c>
@@ -6996,7 +7002,7 @@
         <v>2665.59</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1928</v>
       </c>
@@ -7004,7 +7010,7 @@
         <v>2498.3589999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1929</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1930</v>
       </c>
@@ -7020,7 +7026,7 @@
         <v>2132.8319999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1931</v>
       </c>
@@ -7028,7 +7034,7 @@
         <v>1782.36</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1932</v>
       </c>
@@ -7036,7 +7042,7 @@
         <v>1974.125</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1933</v>
       </c>
@@ -7044,7 +7050,7 @@
         <v>2467.09</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1934</v>
       </c>
@@ -7052,7 +7058,7 @@
         <v>2923.9180000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1935</v>
       </c>
@@ -7060,7 +7066,7 @@
         <v>3479.0949999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1936</v>
       </c>
@@ -7068,7 +7074,7 @@
         <v>3777.0039999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1937</v>
       </c>
@@ -7076,7 +7082,7 @@
         <v>6332.5259999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1938</v>
       </c>
@@ -7084,7 +7090,7 @@
         <v>9641.0889999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1939</v>
       </c>
@@ -7092,7 +7098,7 @@
         <v>12048.315000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1940</v>
       </c>
@@ -7108,9 +7114,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE58F4-EEAA-4770-9857-DC7DBB619D8C}">
   <dimension ref="A1:E104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1868</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>24.036999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1869</v>
       </c>
@@ -7161,7 +7167,7 @@
         <v>50.091000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1870</v>
       </c>
@@ -7178,7 +7184,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1871</v>
       </c>
@@ -7195,7 +7201,7 @@
         <v>72.712999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1872</v>
       </c>
@@ -7212,7 +7218,7 @@
         <v>107.70699999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1873</v>
       </c>
@@ -7229,7 +7235,7 @@
         <v>141.464</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1874</v>
       </c>
@@ -7246,7 +7252,7 @@
         <v>145.79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1875</v>
       </c>
@@ -7263,7 +7269,7 @@
         <v>148.85400000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1876</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>162.286</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1877</v>
       </c>
@@ -7297,7 +7303,7 @@
         <v>175.75800000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1878</v>
       </c>
@@ -7314,7 +7320,7 @@
         <v>219.62100000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1879</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>212.607</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1880</v>
       </c>
@@ -7348,7 +7354,7 @@
         <v>198.85</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1881</v>
       </c>
@@ -7365,7 +7371,7 @@
         <v>191.45500000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1882</v>
       </c>
@@ -7382,7 +7388,7 @@
         <v>186.422</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1883</v>
       </c>
@@ -7399,7 +7405,7 @@
         <v>181.59100000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1884</v>
       </c>
@@ -7416,7 +7422,7 @@
         <v>177.68899999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1885</v>
       </c>
@@ -7433,7 +7439,7 @@
         <v>184.80699999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1886</v>
       </c>
@@ -7450,7 +7456,7 @@
         <v>184.69300000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1887</v>
       </c>
@@ -7467,7 +7473,7 @@
         <v>183.09</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1888</v>
       </c>
@@ -7484,7 +7490,7 @@
         <v>204.92</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1889</v>
       </c>
@@ -7501,7 +7507,7 @@
         <v>214.922</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1890</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>248.095</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1891</v>
       </c>
@@ -7535,7 +7541,7 @@
         <v>245.61199999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1892</v>
       </c>
@@ -7552,7 +7558,7 @@
         <v>261.733</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1893</v>
       </c>
@@ -7569,7 +7575,7 @@
         <v>301.91000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1894</v>
       </c>
@@ -7586,7 +7592,7 @@
         <v>333.84500000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1895</v>
       </c>
@@ -7603,7 +7609,7 @@
         <v>407.21100000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1896</v>
       </c>
@@ -7620,7 +7626,7 @@
         <v>452.101</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1897</v>
       </c>
@@ -7637,7 +7643,7 @@
         <v>518.52599999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1898</v>
       </c>
@@ -7654,7 +7660,7 @@
         <v>532.62599999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1899</v>
       </c>
@@ -7671,7 +7677,7 @@
         <v>718.43</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1900</v>
       </c>
@@ -7688,7 +7694,7 @@
         <v>707.40499999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1901</v>
       </c>
@@ -7705,7 +7711,7 @@
         <v>690.21799999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1902</v>
       </c>
@@ -7722,7 +7728,7 @@
         <v>787.45</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1903</v>
       </c>
@@ -7739,7 +7745,7 @@
         <v>845.60500000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1904</v>
       </c>
@@ -7756,7 +7762,7 @@
         <v>950.22299999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1905</v>
       </c>
@@ -7773,7 +7779,7 @@
         <v>1104.4590000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1906</v>
       </c>
@@ -7790,7 +7796,7 @@
         <v>1461.1110000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1907</v>
       </c>
@@ -7807,7 +7813,7 @@
         <v>1370.8989999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1908</v>
       </c>
@@ -7824,7 +7830,7 @@
         <v>1336.9079999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1909</v>
       </c>
@@ -7841,7 +7847,7 @@
         <v>1499.0709999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1910</v>
       </c>
@@ -7858,7 +7864,7 @@
         <v>1653.7170000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1911</v>
       </c>
@@ -7875,7 +7881,7 @@
         <v>1807.383</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1912</v>
       </c>
@@ -7892,7 +7898,7 @@
         <v>1857.0119999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1913</v>
       </c>
@@ -7909,7 +7915,7 @@
         <v>1840.5719999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1914</v>
       </c>
@@ -7926,7 +7932,7 @@
         <v>1790.663</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1915</v>
       </c>
@@ -7943,7 +7949,7 @@
         <v>2116.8939999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1916</v>
       </c>
@@ -7960,7 +7966,7 @@
         <v>2922.7539999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1917</v>
       </c>
@@ -7977,7 +7983,7 @@
         <v>4186.8100000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1918</v>
       </c>
@@ -7994,7 +8000,7 @@
         <v>5393.8289999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1919</v>
       </c>
@@ -8011,7 +8017,7 @@
         <v>6848.5510000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1920</v>
       </c>
@@ -8028,7 +8034,7 @@
         <v>7356.116</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1921</v>
       </c>
@@ -8045,7 +8051,7 @@
         <v>7913.3649999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1922</v>
       </c>
@@ -8062,7 +8068,7 @@
         <v>7920.8519999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1923</v>
       </c>
@@ -8079,7 +8085,7 @@
         <v>8154.0619999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1924</v>
       </c>
@@ -8096,7 +8102,7 @@
         <v>8126.0770000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1925</v>
       </c>
@@ -8113,7 +8119,7 @@
         <v>8359.8649999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1926</v>
       </c>
@@ -8130,7 +8136,7 @@
         <v>8325.0239999999994</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1927</v>
       </c>
@@ -8147,7 +8153,7 @@
         <v>8850.6110000000008</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1928</v>
       </c>
@@ -8164,7 +8170,7 @@
         <v>9458.2510000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1929</v>
       </c>
@@ -8181,7 +8187,7 @@
         <v>9858.7139999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1930</v>
       </c>
@@ -8198,7 +8204,7 @@
         <v>9515</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1931</v>
       </c>
@@ -8215,7 +8221,7 @@
         <v>9445</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1932</v>
       </c>
@@ -8232,7 +8238,7 @@
         <v>9826</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1933</v>
       </c>
@@ -8249,7 +8255,7 @@
         <v>10458</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1934</v>
       </c>
@@ -8266,7 +8272,7 @@
         <v>11013</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1935</v>
       </c>
@@ -8283,7 +8289,7 @@
         <v>11468</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1936</v>
       </c>
@@ -8300,7 +8306,7 @@
         <v>12668</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1937</v>
       </c>
@@ -8317,7 +8323,7 @@
         <v>15049</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1938</v>
       </c>
@@ -8334,7 +8340,7 @@
         <v>18802</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1939</v>
       </c>
@@ -8351,7 +8357,7 @@
         <v>25955</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1940</v>
       </c>
@@ -8368,7 +8374,7 @@
         <v>33383</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1941</v>
       </c>
@@ -8385,7 +8391,7 @@
         <v>41989</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1942</v>
       </c>
@@ -8402,7 +8408,7 @@
         <v>54259</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1943</v>
       </c>
@@ -8419,7 +8425,7 @@
         <v>71481</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1944</v>
       </c>
@@ -8436,7 +8442,7 @@
         <v>119956</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1945</v>
       </c>
@@ -8450,7 +8456,7 @@
         <v>444970</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1946</v>
       </c>
@@ -8467,7 +8473,7 @@
         <v>315528</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1947</v>
       </c>
@@ -8484,7 +8490,7 @@
         <v>564625</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1948</v>
       </c>
@@ -8501,7 +8507,7 @@
         <v>944020</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1949</v>
       </c>
@@ -8518,7 +8524,7 @@
         <v>1106566</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1950</v>
       </c>
@@ -8535,7 +8541,7 @@
         <v>1328339</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1951</v>
       </c>
@@ -8552,7 +8558,7 @@
         <v>1753416</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1952</v>
       </c>
@@ -8569,7 +8575,7 @@
         <v>2303626</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1953</v>
       </c>
@@ -8586,7 +8592,7 @@
         <v>2649706</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1954</v>
       </c>
@@ -8603,7 +8609,7 @@
         <v>2811572</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1955</v>
       </c>
@@ -8620,7 +8626,7 @@
         <v>3232086</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1956</v>
       </c>
@@ -8637,7 +8643,7 @@
         <v>3998704</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1957</v>
       </c>
@@ -8654,7 +8660,7 @@
         <v>4357722</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1958</v>
       </c>
@@ -8671,7 +8677,7 @@
         <v>4825404</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1959</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>5345504</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1960</v>
       </c>
@@ -8705,7 +8711,7 @@
         <v>6420206</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1961</v>
       </c>
@@ -8722,7 +8728,7 @@
         <v>7730647</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1962</v>
       </c>
@@ -8739,7 +8745,7 @@
         <v>9126471</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1963</v>
       </c>
@@ -8756,7 +8762,7 @@
         <v>12082710</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1964</v>
       </c>
@@ -8773,7 +8779,7 @@
         <v>14044716</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1965</v>
       </c>
@@ -8790,7 +8796,7 @@
         <v>15855277</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1966</v>
       </c>
@@ -8807,7 +8813,7 @@
         <v>18115200</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1967</v>
       </c>
@@ -8824,7 +8830,7 @@
         <v>20609900</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1968</v>
       </c>
@@ -8841,7 +8847,7 @@
         <v>23489100</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1969</v>
       </c>
@@ -8858,7 +8864,7 @@
         <v>28129800</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1970</v>
       </c>
@@ -8883,9 +8889,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389619B2-8C06-4157-888E-660CCCB86FF3}">
   <dimension ref="A1:D87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8899,7 +8908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1875</v>
       </c>
@@ -8913,7 +8922,7 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1876</v>
       </c>
@@ -8927,7 +8936,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1877</v>
       </c>
@@ -8941,7 +8950,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1878</v>
       </c>
@@ -8955,7 +8964,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1879</v>
       </c>
@@ -8969,7 +8978,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1880</v>
       </c>
@@ -8983,7 +8992,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1881</v>
       </c>
@@ -8997,7 +9006,7 @@
         <v>66.2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1882</v>
       </c>
@@ -9011,7 +9020,7 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1883</v>
       </c>
@@ -9025,7 +9034,7 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1884</v>
       </c>
@@ -9039,7 +9048,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1885</v>
       </c>
@@ -9053,7 +9062,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1886</v>
       </c>
@@ -9067,7 +9076,7 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1887</v>
       </c>
@@ -9081,7 +9090,7 @@
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1888</v>
       </c>
@@ -9095,7 +9104,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1889</v>
       </c>
@@ -9109,7 +9118,7 @@
         <v>81.2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1890</v>
       </c>
@@ -9123,7 +9132,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1891</v>
       </c>
@@ -9137,7 +9146,7 @@
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1892</v>
       </c>
@@ -9151,7 +9160,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1893</v>
       </c>
@@ -9165,7 +9174,7 @@
         <v>81.099999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1894</v>
       </c>
@@ -9179,7 +9188,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1895</v>
       </c>
@@ -9193,7 +9202,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1896</v>
       </c>
@@ -9207,7 +9216,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1897</v>
       </c>
@@ -9221,7 +9230,7 @@
         <v>104.7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1898</v>
       </c>
@@ -9235,7 +9244,7 @@
         <v>126.8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1899</v>
       </c>
@@ -9249,7 +9258,7 @@
         <v>163.80000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1900</v>
       </c>
@@ -9263,7 +9272,7 @@
         <v>174.2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1901</v>
       </c>
@@ -9277,7 +9286,7 @@
         <v>190.2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1902</v>
       </c>
@@ -9291,7 +9300,7 @@
         <v>206.1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1903</v>
       </c>
@@ -9305,7 +9314,7 @@
         <v>207.7</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1904</v>
       </c>
@@ -9319,7 +9328,7 @@
         <v>283.2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1905</v>
       </c>
@@ -9333,7 +9342,7 @@
         <v>375.2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1906</v>
       </c>
@@ -9347,7 +9356,7 @@
         <v>431.9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1907</v>
       </c>
@@ -9361,7 +9370,7 @@
         <v>490.8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1908</v>
       </c>
@@ -9375,7 +9384,7 @@
         <v>493.3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1909</v>
       </c>
@@ -9389,7 +9398,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1910</v>
       </c>
@@ -9403,7 +9412,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1911</v>
       </c>
@@ -9417,7 +9426,7 @@
         <v>500.4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1912</v>
       </c>
@@ -9431,7 +9440,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1913</v>
       </c>
@@ -9445,7 +9454,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1914</v>
       </c>
@@ -9459,7 +9468,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1915</v>
       </c>
@@ -9473,7 +9482,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1916</v>
       </c>
@@ -9487,7 +9496,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1917</v>
       </c>
@@ -9501,7 +9510,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1918</v>
       </c>
@@ -9515,7 +9524,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1919</v>
       </c>
@@ -9529,7 +9538,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1920</v>
       </c>
@@ -9543,7 +9552,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1921</v>
       </c>
@@ -9557,7 +9566,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1922</v>
       </c>
@@ -9571,7 +9580,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1923</v>
       </c>
@@ -9585,7 +9594,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1924</v>
       </c>
@@ -9599,7 +9608,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1925</v>
       </c>
@@ -9613,7 +9622,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1926</v>
       </c>
@@ -9627,7 +9636,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1927</v>
       </c>
@@ -9641,7 +9650,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1928</v>
       </c>
@@ -9655,7 +9664,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1929</v>
       </c>
@@ -9669,7 +9678,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1930</v>
       </c>
@@ -9677,7 +9686,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1931</v>
       </c>
@@ -9685,7 +9694,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1932</v>
       </c>
@@ -9693,7 +9702,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1933</v>
       </c>
@@ -9701,7 +9710,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1934</v>
       </c>
@@ -9709,7 +9718,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1935</v>
       </c>
@@ -9717,7 +9726,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1936</v>
       </c>
@@ -9725,7 +9734,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1937</v>
       </c>
@@ -9733,7 +9742,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1938</v>
       </c>
@@ -9741,7 +9750,7 @@
         <v>3288</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1939</v>
       </c>
@@ -9749,7 +9758,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1940</v>
       </c>
@@ -9757,7 +9766,7 @@
         <v>5860</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1941</v>
       </c>
@@ -9765,7 +9774,7 @@
         <v>8134</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1942</v>
       </c>
@@ -9773,7 +9782,7 @@
         <v>8276</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1943</v>
       </c>
@@ -9781,7 +9790,7 @@
         <v>12552</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1944</v>
       </c>
@@ -9789,7 +9798,7 @@
         <v>19872</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1945</v>
       </c>
@@ -9797,7 +9806,7 @@
         <v>21496</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1946</v>
       </c>
@@ -9805,7 +9814,7 @@
         <v>1152000</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1947</v>
       </c>
@@ -9813,7 +9822,7 @@
         <v>2058000</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1948</v>
       </c>
@@ -9821,7 +9830,7 @@
         <v>4620000</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1949</v>
       </c>
@@ -9829,7 +9838,7 @@
         <v>6994000</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1950</v>
       </c>
@@ -9837,7 +9846,7 @@
         <v>6333000</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1951</v>
       </c>
@@ -9845,7 +9854,7 @@
         <v>7498000</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1952</v>
       </c>
@@ -9853,7 +9862,7 @@
         <v>8739000</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1953</v>
       </c>
@@ -9861,7 +9870,7 @@
         <v>10172000</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1954</v>
       </c>
@@ -9869,7 +9878,7 @@
         <v>10408000</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1955</v>
       </c>
@@ -9877,7 +9886,7 @@
         <v>10182000</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1956</v>
       </c>
@@ -9885,7 +9894,7 @@
         <v>10692000</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1957</v>
       </c>
@@ -9893,7 +9902,7 @@
         <v>11877000</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1958</v>
       </c>
@@ -9901,7 +9910,7 @@
         <v>13316000</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1959</v>
       </c>
@@ -9909,7 +9918,7 @@
         <v>14950000</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1960</v>
       </c>
@@ -9925,9 +9934,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9C6456-4998-412E-B8CD-4421ED73B8D3}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9935,7 +9944,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1879</v>
       </c>
@@ -9943,7 +9952,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1880</v>
       </c>
@@ -9951,7 +9960,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1881</v>
       </c>
@@ -9959,7 +9968,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1882</v>
       </c>
@@ -9967,7 +9976,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1883</v>
       </c>
@@ -9975,7 +9984,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1884</v>
       </c>
@@ -9983,7 +9992,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1885</v>
       </c>
@@ -9991,7 +10000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1886</v>
       </c>
@@ -9999,7 +10008,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1887</v>
       </c>
@@ -10007,7 +10016,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1888</v>
       </c>
@@ -10015,7 +10024,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1889</v>
       </c>
@@ -10023,7 +10032,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1890</v>
       </c>
@@ -10031,7 +10040,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1891</v>
       </c>
@@ -10039,7 +10048,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1892</v>
       </c>
@@ -10047,7 +10056,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1893</v>
       </c>
@@ -10055,7 +10064,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1894</v>
       </c>
@@ -10063,7 +10072,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1895</v>
       </c>
@@ -10071,7 +10080,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1896</v>
       </c>
@@ -10079,7 +10088,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1897</v>
       </c>
@@ -10087,7 +10096,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1898</v>
       </c>
@@ -10095,7 +10104,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1899</v>
       </c>
@@ -10103,7 +10112,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1900</v>
       </c>
@@ -10111,7 +10120,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1901</v>
       </c>
@@ -10119,7 +10128,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1902</v>
       </c>
@@ -10127,7 +10136,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1903</v>
       </c>
@@ -10135,7 +10144,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1904</v>
       </c>
@@ -10143,7 +10152,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1905</v>
       </c>
@@ -10151,7 +10160,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1906</v>
       </c>
@@ -10159,7 +10168,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1907</v>
       </c>
@@ -10167,7 +10176,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1908</v>
       </c>
@@ -10175,7 +10184,7 @@
         <v>59.9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1909</v>
       </c>
@@ -10183,7 +10192,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1910</v>
       </c>
@@ -10191,7 +10200,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1911</v>
       </c>
@@ -10199,7 +10208,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1912</v>
       </c>
@@ -10207,7 +10216,7 @@
         <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1913</v>
       </c>
@@ -10215,7 +10224,7 @@
         <v>66.900000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1914</v>
       </c>
@@ -10223,7 +10232,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1915</v>
       </c>
@@ -10231,7 +10240,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1916</v>
       </c>
@@ -10239,7 +10248,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1917</v>
       </c>
@@ -10247,7 +10256,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1918</v>
       </c>
@@ -10255,7 +10264,7 @@
         <v>106.6</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1919</v>
       </c>
@@ -10263,7 +10272,7 @@
         <v>137.69999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1920</v>
       </c>
@@ -10271,7 +10280,7 @@
         <v>147.4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1921</v>
       </c>
@@ -10279,7 +10288,7 @@
         <v>133.4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1922</v>
       </c>
@@ -10287,7 +10296,7 @@
         <v>131.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1923</v>
       </c>
@@ -10295,7 +10304,7 @@
         <v>130.80000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1924</v>
       </c>
@@ -10303,7 +10312,7 @@
         <v>131.6</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1925</v>
       </c>
@@ -10311,7 +10320,7 @@
         <v>131.30000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1926</v>
       </c>
@@ -10319,7 +10328,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1927</v>
       </c>
@@ -10327,7 +10336,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1928</v>
       </c>
@@ -10335,7 +10344,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1929</v>
       </c>
@@ -10343,7 +10352,7 @@
         <v>116.2</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1930</v>
       </c>
@@ -10351,7 +10360,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1931</v>
       </c>
@@ -10359,7 +10368,7 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1932</v>
       </c>
@@ -10367,7 +10376,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1933</v>
       </c>
@@ -10375,7 +10384,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1934</v>
       </c>
@@ -10383,7 +10392,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1935</v>
       </c>
@@ -10391,7 +10400,7 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1936</v>
       </c>
@@ -10399,7 +10408,7 @@
         <v>102.3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1937</v>
       </c>
@@ -10407,7 +10416,7 @@
         <v>112.9</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1938</v>
       </c>
@@ -10423,9 +10432,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06EE4FA-7404-4586-8990-F40CC1D236DB}">
   <dimension ref="A1:D99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10439,7 +10448,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1873</v>
       </c>
@@ -10450,7 +10459,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1874</v>
       </c>
@@ -10464,7 +10473,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1875</v>
       </c>
@@ -10478,7 +10487,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1876</v>
       </c>
@@ -10492,7 +10501,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1877</v>
       </c>
@@ -10506,7 +10515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1878</v>
       </c>
@@ -10520,7 +10529,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1879</v>
       </c>
@@ -10534,7 +10543,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1880</v>
       </c>
@@ -10548,7 +10557,7 @@
         <v>95.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1881</v>
       </c>
@@ -10562,7 +10571,7 @@
         <v>91.25</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1882</v>
       </c>
@@ -10576,7 +10585,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1883</v>
       </c>
@@ -10590,7 +10599,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1884</v>
       </c>
@@ -10604,7 +10613,7 @@
         <v>90.75</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1885</v>
       </c>
@@ -10618,7 +10627,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1886</v>
       </c>
@@ -10632,7 +10641,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1887</v>
       </c>
@@ -10646,7 +10655,7 @@
         <v>80.25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1888</v>
       </c>
@@ -10660,7 +10669,7 @@
         <v>76.25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1889</v>
       </c>
@@ -10674,7 +10683,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1890</v>
       </c>
@@ -10688,7 +10697,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1891</v>
       </c>
@@ -10702,7 +10711,7 @@
         <v>84.75</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1892</v>
       </c>
@@ -10716,7 +10725,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1893</v>
       </c>
@@ -10730,7 +10739,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1894</v>
       </c>
@@ -10744,7 +10753,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1895</v>
       </c>
@@ -10758,7 +10767,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1896</v>
       </c>
@@ -10772,7 +10781,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1897</v>
       </c>
@@ -10786,7 +10795,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1898</v>
       </c>
@@ -10800,7 +10809,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1899</v>
       </c>
@@ -10814,7 +10823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1900</v>
       </c>
@@ -10828,7 +10837,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1901</v>
       </c>
@@ -10842,7 +10851,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1902</v>
       </c>
@@ -10856,7 +10865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1903</v>
       </c>
@@ -10870,7 +10879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1904</v>
       </c>
@@ -10884,7 +10893,7 @@
         <v>49.25</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1905</v>
       </c>
@@ -10898,7 +10907,7 @@
         <v>49.875</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1906</v>
       </c>
@@ -10912,7 +10921,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1907</v>
       </c>
@@ -10926,7 +10935,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1908</v>
       </c>
@@ -10940,7 +10949,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1909</v>
       </c>
@@ -10954,7 +10963,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1910</v>
       </c>
@@ -10968,7 +10977,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1911</v>
       </c>
@@ -10982,7 +10991,7 @@
         <v>49.375</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1912</v>
       </c>
@@ -10996,7 +11005,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1913</v>
       </c>
@@ -11010,7 +11019,7 @@
         <v>49.625</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1914</v>
       </c>
@@ -11024,7 +11033,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1915</v>
       </c>
@@ -11038,7 +11047,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1916</v>
       </c>
@@ -11052,7 +11061,7 @@
         <v>50.375</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1917</v>
       </c>
@@ -11066,7 +11075,7 @@
         <v>50.875</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1918</v>
       </c>
@@ -11080,7 +11089,7 @@
         <v>52.125</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1919</v>
       </c>
@@ -11094,7 +11103,7 @@
         <v>51.875</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1920</v>
       </c>
@@ -11108,7 +11117,7 @@
         <v>50.625</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1921</v>
       </c>
@@ -11122,7 +11131,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1922</v>
       </c>
@@ -11136,7 +11145,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1923</v>
       </c>
@@ -11150,7 +11159,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1924</v>
       </c>
@@ -11164,7 +11173,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1925</v>
       </c>
@@ -11178,7 +11187,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1926</v>
       </c>
@@ -11192,7 +11201,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1927</v>
       </c>
@@ -11206,7 +11215,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1928</v>
       </c>
@@ -11220,7 +11229,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1929</v>
       </c>
@@ -11234,7 +11243,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1930</v>
       </c>
@@ -11248,7 +11257,7 @@
         <v>49.375</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1931</v>
       </c>
@@ -11262,7 +11271,7 @@
         <v>49.375</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1932</v>
       </c>
@@ -11276,7 +11285,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1933</v>
       </c>
@@ -11290,7 +11299,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1934</v>
       </c>
@@ -11304,7 +11313,7 @@
         <v>30.375</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1935</v>
       </c>
@@ -11318,7 +11327,7 @@
         <v>29.125</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1936</v>
       </c>
@@ -11332,7 +11341,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1937</v>
       </c>
@@ -11346,7 +11355,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1938</v>
       </c>
@@ -11360,7 +11369,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1939</v>
       </c>
@@ -11374,7 +11383,7 @@
         <v>27.375</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1940</v>
       </c>
@@ -11385,57 +11394,57 @@
         <v>4652.8</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1941</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1942</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1943</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1944</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1945</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1946</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1947</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1948</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1949</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1950</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1951</v>
       </c>
@@ -11446,7 +11455,7 @@
         <v>735700</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1952</v>
       </c>
@@ -11457,7 +11466,7 @@
         <v>727300</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1953</v>
       </c>
@@ -11468,7 +11477,7 @@
         <v>862300</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1954</v>
       </c>
@@ -11479,7 +11488,7 @@
         <v>860100</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1955</v>
       </c>
@@ -11490,7 +11499,7 @@
         <v>884000</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1956</v>
       </c>
@@ -11501,7 +11510,7 @@
         <v>1154700</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1957</v>
       </c>
@@ -11512,7 +11521,7 @@
         <v>1535900</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1958</v>
       </c>
@@ -11523,7 +11532,7 @@
         <v>1086400</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1959</v>
       </c>
@@ -11534,7 +11543,7 @@
         <v>1288600</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1960</v>
       </c>
@@ -11545,7 +11554,7 @@
         <v>1607200</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1961</v>
       </c>
@@ -11556,7 +11565,7 @@
         <v>2103400</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1962</v>
       </c>
@@ -11567,7 +11576,7 @@
         <v>2013100</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1963</v>
       </c>
@@ -11578,7 +11587,7 @@
         <v>2401900</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1964</v>
       </c>
@@ -11589,7 +11598,7 @@
         <v>2834500</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1965</v>
       </c>
@@ -11600,7 +11609,7 @@
         <v>2911200</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1966</v>
       </c>
@@ -11611,7 +11620,7 @@
         <v>3399900</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1967</v>
       </c>
@@ -11622,7 +11631,7 @@
         <v>4170800</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1968</v>
       </c>
@@ -11633,7 +11642,7 @@
         <v>4643500</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1969</v>
       </c>
@@ -11644,7 +11653,7 @@
         <v>5374800</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1970</v>
       </c>
@@ -11661,20 +11670,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3a75076d-6340-48f6-9ad9-e0e5c3f8ac62" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3a75076d-6340-48f6-9ad9-e0e5c3f8ac62" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11834,6 +11843,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5FD250D-C4E7-4BAF-93F0-39C302D43D43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B07C7BB-3DB2-42F9-97E7-9321B78EF00C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -11845,14 +11862,6 @@
     <ds:schemaRef ds:uri="3a75076d-6340-48f6-9ad9-e0e5c3f8ac62"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5FD250D-C4E7-4BAF-93F0-39C302D43D43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
